--- a/data/testdata.xlsx
+++ b/data/testdata.xlsx
@@ -28,7 +28,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
+  <si>
+    <t>用例编号</t>
+  </si>
+  <si>
+    <t>模块</t>
+  </si>
+  <si>
+    <t>场景</t>
+  </si>
+  <si>
+    <t>标题</t>
+  </si>
   <si>
     <t>请求方式</t>
   </si>
@@ -51,9 +63,39 @@
     <t>文件参数</t>
   </si>
   <si>
+    <t>校验字段</t>
+  </si>
+  <si>
     <t>预期结果</t>
   </si>
   <si>
+    <t>数据库校验内容</t>
+  </si>
+  <si>
+    <t>数据库预期结果</t>
+  </si>
+  <si>
+    <t>json提取</t>
+  </si>
+  <si>
+    <t>sql提取</t>
+  </si>
+  <si>
+    <t>是否执行</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>feature</t>
+  </si>
+  <si>
+    <t>story</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
     <t>method</t>
   </si>
   <si>
@@ -75,7 +117,34 @@
     <t>files</t>
   </si>
   <si>
-    <t>excepted</t>
+    <t>check</t>
+  </si>
+  <si>
+    <t>expected</t>
+  </si>
+  <si>
+    <t>sql_check</t>
+  </si>
+  <si>
+    <t>sql_expectted</t>
+  </si>
+  <si>
+    <t>jsonExdata</t>
+  </si>
+  <si>
+    <t>sqlExdata</t>
+  </si>
+  <si>
+    <t>is_True</t>
+  </si>
+  <si>
+    <t>登录</t>
+  </si>
+  <si>
+    <t>登录成功</t>
+  </si>
+  <si>
+    <t>管理员登录成功</t>
   </si>
   <si>
     <t>post</t>
@@ -87,7 +156,28 @@
     <t>{'username':'admin','paswword':'admin'}</t>
   </si>
   <si>
-    <t>登录成功</t>
+    <t>$..msg</t>
+  </si>
+  <si>
+    <t>select mg_name from sp_manager where mg_name = 'admin'</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>{"TOKEN": "$..token"}</t>
+  </si>
+  <si>
+    <t>{"admin":''select mg_name from sp_manager where mg_name='admin'"}</t>
+  </si>
+  <si>
+    <t>用户管理</t>
+  </si>
+  <si>
+    <t>查询失败</t>
+  </si>
+  <si>
+    <t>未登录状态查询用户列表失败</t>
   </si>
   <si>
     <t>get</t>
@@ -112,9 +202,25 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -466,12 +572,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -592,145 +713,160 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1257,15 +1393,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="7"/>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col min="4" max="4" width="41.9807692307692" customWidth="1"/>
     <col min="5" max="5" width="30.2788461538462" customWidth="1"/>
     <col min="6" max="6" width="28.2019230769231" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:8">
+    <row r="1" ht="36" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1281,76 +1417,186 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" ht="18" spans="1:8">
+    <row r="2" ht="18" spans="1:18">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="3" ht="36" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" t="s">
-        <v>19</v>
+    <row r="3" ht="88" spans="1:18">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" s="4" t="b">
+        <v>1</v>
       </c>
     </row>
-    <row r="4" ht="17.6" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" t="s">
-        <v>23</v>
+    <row r="4" ht="17.6" spans="1:18">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
